--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -445,7 +445,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.519478260869567</v>
+        <v>3.499741379310346</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3715046783874216</v>
+        <v>0.3688166062876869</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.473577226931443</v>
+        <v>9.489110087902208</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.5241488622315456</v>
+        <v>0.518969354785811</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.714654012384022</v>
+        <v>6.743637841110598</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3882041321353366</v>
+        <v>0.3857634519698406</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.150522391674688</v>
+        <v>9.162719274570497</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5791256161049186</v>
+        <v>0.5751283038247289</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.133851628834669</v>
+        <v>6.14583249212874</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08305537019862617</v>
+        <v>0.08276917989976497</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.3047363335850518</v>
+        <v>-0.32238934500741</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1058495973296158</v>
+        <v>0.1057831234614072</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2391127565659335</v>
+        <v>-0.2522510285340628</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +597,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Newey-West Inference.xlsx
+++ b/isolated_excel/Newey-West Inference.xlsx
@@ -445,7 +445,7 @@
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,19 +487,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.499741379310346</v>
+        <v>3.479145299145302</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3688166062876869</v>
+        <v>0.3662303402743725</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.489110087902208</v>
+        <v>9.499882769239695</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.518969354785811</v>
+        <v>0.5149206796216128</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6.743637841110598</v>
+        <v>6.756662602290388</v>
       </c>
     </row>
     <row r="3">
@@ -509,19 +509,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.3857634519698406</v>
+        <v>0.3828516705792904</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9.162719274570497</v>
+        <v>9.171774840692462</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0.5751283038247289</v>
+        <v>0.5698893582375369</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>6.14583249212874</v>
+        <v>6.161598333395458</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.08276917989976497</v>
+        <v>0.08249578451452012</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-0.32238934500741</v>
+        <v>-0.3024738953513129</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0.1057831234614072</v>
+        <v>0.1057404898472523</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>-0.2522510285340628</v>
+        <v>-0.23598170699053</v>
       </c>
     </row>
   </sheetData>
@@ -597,7 +597,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
